--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118846916</v>
+        <v>118846909</v>
       </c>
       <c r="B2" t="n">
-        <v>97880</v>
+        <v>90788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555112</v>
+        <v>555016</v>
       </c>
       <c r="R2" t="n">
-        <v>7013394</v>
+        <v>7013452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118846918</v>
+        <v>118846920</v>
       </c>
       <c r="B3" t="n">
-        <v>102758</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555131</v>
+        <v>555203</v>
       </c>
       <c r="R3" t="n">
-        <v>7013394</v>
+        <v>7013382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118846924</v>
+        <v>118846914</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555203</v>
+        <v>555055</v>
       </c>
       <c r="R4" t="n">
-        <v>7013382</v>
+        <v>7013432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118846905</v>
+        <v>118846915</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555159</v>
+        <v>555058</v>
       </c>
       <c r="R5" t="n">
-        <v>7013354</v>
+        <v>7013476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846906</v>
+        <v>118846905</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>90788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846907</v>
+        <v>118846919</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
+        <v>100107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555159</v>
+        <v>555131</v>
       </c>
       <c r="R8" t="n">
-        <v>7013354</v>
+        <v>7013394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846910</v>
+        <v>118846924</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555016</v>
+        <v>555203</v>
       </c>
       <c r="R9" t="n">
-        <v>7013452</v>
+        <v>7013382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118846919</v>
+        <v>118846906</v>
       </c>
       <c r="B10" t="n">
-        <v>100107</v>
+        <v>79600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555131</v>
+        <v>555159</v>
       </c>
       <c r="R10" t="n">
-        <v>7013394</v>
+        <v>7013354</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118846909</v>
+        <v>118846910</v>
       </c>
       <c r="B11" t="n">
-        <v>90788</v>
+        <v>90504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118846915</v>
+        <v>118846912</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555058</v>
+        <v>554979</v>
       </c>
       <c r="R12" t="n">
-        <v>7013476</v>
+        <v>7013460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846920</v>
+        <v>118846907</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555203</v>
+        <v>555159</v>
       </c>
       <c r="R13" t="n">
-        <v>7013382</v>
+        <v>7013354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118846914</v>
+        <v>118846918</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>102758</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>222002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555055</v>
+        <v>555131</v>
       </c>
       <c r="R14" t="n">
-        <v>7013432</v>
+        <v>7013394</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118846912</v>
+        <v>118846916</v>
       </c>
       <c r="B15" t="n">
-        <v>78221</v>
+        <v>97880</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>219874</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554979</v>
+        <v>555112</v>
       </c>
       <c r="R15" t="n">
-        <v>7013460</v>
+        <v>7013394</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846905</v>
+        <v>118846913</v>
       </c>
       <c r="B6" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555159</v>
+        <v>555063</v>
       </c>
       <c r="R6" t="n">
-        <v>7013354</v>
+        <v>7013433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118846913</v>
+        <v>118846905</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555063</v>
+        <v>555159</v>
       </c>
       <c r="R7" t="n">
-        <v>7013433</v>
+        <v>7013354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846919</v>
+        <v>118846924</v>
       </c>
       <c r="B8" t="n">
-        <v>100107</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555131</v>
+        <v>555203</v>
       </c>
       <c r="R8" t="n">
-        <v>7013394</v>
+        <v>7013382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846924</v>
+        <v>118846919</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>100107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555203</v>
+        <v>555131</v>
       </c>
       <c r="R9" t="n">
-        <v>7013382</v>
+        <v>7013394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118846912</v>
+        <v>118846907</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
+        <v>79565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554979</v>
+        <v>555159</v>
       </c>
       <c r="R12" t="n">
-        <v>7013460</v>
+        <v>7013354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846907</v>
+        <v>118846912</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>78221</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555159</v>
+        <v>554979</v>
       </c>
       <c r="R13" t="n">
-        <v>7013354</v>
+        <v>7013460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118846920</v>
+        <v>118846907</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555203</v>
+        <v>555159</v>
       </c>
       <c r="R3" t="n">
-        <v>7013382</v>
+        <v>7013354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118846915</v>
+        <v>118846912</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555058</v>
+        <v>554979</v>
       </c>
       <c r="R5" t="n">
-        <v>7013476</v>
+        <v>7013460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846913</v>
+        <v>118846906</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>79600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555063</v>
+        <v>555159</v>
       </c>
       <c r="R6" t="n">
-        <v>7013433</v>
+        <v>7013354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118846905</v>
+        <v>118846924</v>
       </c>
       <c r="B7" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555159</v>
+        <v>555203</v>
       </c>
       <c r="R7" t="n">
-        <v>7013354</v>
+        <v>7013382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846924</v>
+        <v>118846913</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555203</v>
+        <v>555063</v>
       </c>
       <c r="R8" t="n">
-        <v>7013382</v>
+        <v>7013433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846919</v>
+        <v>118846910</v>
       </c>
       <c r="B9" t="n">
-        <v>100107</v>
+        <v>90504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555131</v>
+        <v>555016</v>
       </c>
       <c r="R9" t="n">
-        <v>7013394</v>
+        <v>7013452</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118846906</v>
+        <v>118846919</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>100107</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555159</v>
+        <v>555131</v>
       </c>
       <c r="R10" t="n">
-        <v>7013354</v>
+        <v>7013394</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118846910</v>
+        <v>118846920</v>
       </c>
       <c r="B11" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555016</v>
+        <v>555203</v>
       </c>
       <c r="R11" t="n">
-        <v>7013452</v>
+        <v>7013382</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118846907</v>
+        <v>118846915</v>
       </c>
       <c r="B12" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555159</v>
+        <v>555058</v>
       </c>
       <c r="R12" t="n">
-        <v>7013354</v>
+        <v>7013476</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846912</v>
+        <v>118846905</v>
       </c>
       <c r="B13" t="n">
-        <v>78221</v>
+        <v>90788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554979</v>
+        <v>555159</v>
       </c>
       <c r="R13" t="n">
-        <v>7013460</v>
+        <v>7013354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118846909</v>
+        <v>118846920</v>
       </c>
       <c r="B2" t="n">
-        <v>90788</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555016</v>
+        <v>555203</v>
       </c>
       <c r="R2" t="n">
-        <v>7013452</v>
+        <v>7013382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118846907</v>
+        <v>118846913</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555159</v>
+        <v>555063</v>
       </c>
       <c r="R3" t="n">
-        <v>7013354</v>
+        <v>7013433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>118846914</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118846912</v>
+        <v>118846906</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554979</v>
+        <v>555159</v>
       </c>
       <c r="R5" t="n">
-        <v>7013460</v>
+        <v>7013354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846906</v>
+        <v>118846907</v>
       </c>
       <c r="B6" t="n">
-        <v>79600</v>
+        <v>79572</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118846924</v>
+        <v>118846910</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555203</v>
+        <v>555016</v>
       </c>
       <c r="R7" t="n">
-        <v>7013382</v>
+        <v>7013452</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846913</v>
+        <v>118846905</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>90795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555063</v>
+        <v>555159</v>
       </c>
       <c r="R8" t="n">
-        <v>7013433</v>
+        <v>7013354</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846910</v>
+        <v>118846909</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>90795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118846919</v>
+        <v>118846924</v>
       </c>
       <c r="B10" t="n">
-        <v>100107</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555131</v>
+        <v>555203</v>
       </c>
       <c r="R10" t="n">
-        <v>7013394</v>
+        <v>7013382</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118846920</v>
+        <v>118846915</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555203</v>
+        <v>555058</v>
       </c>
       <c r="R11" t="n">
-        <v>7013382</v>
+        <v>7013476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118846915</v>
+        <v>118846919</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>100114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555058</v>
+        <v>555131</v>
       </c>
       <c r="R12" t="n">
-        <v>7013476</v>
+        <v>7013394</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846905</v>
+        <v>118846912</v>
       </c>
       <c r="B13" t="n">
-        <v>90788</v>
+        <v>78228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555159</v>
+        <v>554979</v>
       </c>
       <c r="R13" t="n">
-        <v>7013354</v>
+        <v>7013460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118846918</v>
+        <v>118846916</v>
       </c>
       <c r="B14" t="n">
-        <v>102758</v>
+        <v>97887</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222002</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555131</v>
+        <v>555112</v>
       </c>
       <c r="R14" t="n">
         <v>7013394</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118846916</v>
+        <v>118846918</v>
       </c>
       <c r="B15" t="n">
-        <v>97880</v>
+        <v>102765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>222002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555112</v>
+        <v>555131</v>
       </c>
       <c r="R15" t="n">
         <v>7013394</v>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118846920</v>
+        <v>118846924</v>
       </c>
       <c r="B2" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118846913</v>
+        <v>118846909</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555063</v>
+        <v>555016</v>
       </c>
       <c r="R3" t="n">
-        <v>7013433</v>
+        <v>7013452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118846914</v>
+        <v>118846913</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555055</v>
+        <v>555063</v>
       </c>
       <c r="R4" t="n">
-        <v>7013432</v>
+        <v>7013433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118846906</v>
+        <v>118846910</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>90511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555159</v>
+        <v>555016</v>
       </c>
       <c r="R5" t="n">
-        <v>7013354</v>
+        <v>7013452</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846907</v>
+        <v>118846912</v>
       </c>
       <c r="B6" t="n">
-        <v>79572</v>
+        <v>78228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555159</v>
+        <v>554979</v>
       </c>
       <c r="R6" t="n">
-        <v>7013354</v>
+        <v>7013460</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118846910</v>
+        <v>118846905</v>
       </c>
       <c r="B7" t="n">
-        <v>90511</v>
+        <v>90795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555016</v>
+        <v>555159</v>
       </c>
       <c r="R7" t="n">
-        <v>7013452</v>
+        <v>7013354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846905</v>
+        <v>118846907</v>
       </c>
       <c r="B8" t="n">
-        <v>90795</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846909</v>
+        <v>118846906</v>
       </c>
       <c r="B9" t="n">
-        <v>90795</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555016</v>
+        <v>555159</v>
       </c>
       <c r="R9" t="n">
-        <v>7013452</v>
+        <v>7013354</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118846924</v>
+        <v>118846914</v>
       </c>
       <c r="B10" t="n">
         <v>97853</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555203</v>
+        <v>555055</v>
       </c>
       <c r="R10" t="n">
-        <v>7013382</v>
+        <v>7013432</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118846915</v>
+        <v>118846920</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555058</v>
+        <v>555203</v>
       </c>
       <c r="R11" t="n">
-        <v>7013476</v>
+        <v>7013382</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846912</v>
+        <v>118846915</v>
       </c>
       <c r="B13" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554979</v>
+        <v>555058</v>
       </c>
       <c r="R13" t="n">
-        <v>7013460</v>
+        <v>7013476</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118846914</v>
+        <v>118846905</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555055</v>
+        <v>555159</v>
       </c>
       <c r="R2" t="n">
-        <v>7013432</v>
+        <v>7013354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118846920</v>
+        <v>118846909</v>
       </c>
       <c r="B3" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555203</v>
+        <v>555016</v>
       </c>
       <c r="R3" t="n">
-        <v>7013382</v>
+        <v>7013452</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118846907</v>
+        <v>118846910</v>
       </c>
       <c r="B4" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555159</v>
+        <v>555016</v>
       </c>
       <c r="R4" t="n">
-        <v>7013354</v>
+        <v>7013452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118846912</v>
+        <v>118846920</v>
       </c>
       <c r="B5" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554979</v>
+        <v>555203</v>
       </c>
       <c r="R5" t="n">
-        <v>7013460</v>
+        <v>7013382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118846905</v>
+        <v>118846907</v>
       </c>
       <c r="B6" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118846913</v>
+        <v>118846906</v>
       </c>
       <c r="B7" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555063</v>
+        <v>555159</v>
       </c>
       <c r="R7" t="n">
-        <v>7013433</v>
+        <v>7013354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118846909</v>
+        <v>118846916</v>
       </c>
       <c r="B8" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555016</v>
+        <v>555112</v>
       </c>
       <c r="R8" t="n">
-        <v>7013452</v>
+        <v>7013394</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118846910</v>
+        <v>118846913</v>
       </c>
       <c r="B9" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555016</v>
+        <v>555063</v>
       </c>
       <c r="R9" t="n">
-        <v>7013452</v>
+        <v>7013433</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118846919</v>
+        <v>118846914</v>
       </c>
       <c r="B10" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555131</v>
+        <v>555055</v>
       </c>
       <c r="R10" t="n">
-        <v>7013394</v>
+        <v>7013432</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,12 +1551,7 @@
         <v>118846915</v>
       </c>
       <c r="B11" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118846906</v>
+        <v>118846924</v>
       </c>
       <c r="B12" t="n">
-        <v>79609</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555159</v>
+        <v>555203</v>
       </c>
       <c r="R12" t="n">
-        <v>7013354</v>
+        <v>7013382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118846924</v>
+        <v>118846926</v>
       </c>
       <c r="B13" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555203</v>
+        <v>555220</v>
       </c>
       <c r="R13" t="n">
-        <v>7013382</v>
+        <v>7013394</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,12 +1842,7 @@
         <v>118846918</v>
       </c>
       <c r="B14" t="n">
-        <v>102770</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118846916</v>
+        <v>118846919</v>
       </c>
       <c r="B15" t="n">
-        <v>97892</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219874</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +1971,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555112</v>
+        <v>555131</v>
       </c>
       <c r="R15" t="n">
         <v>7013394</v>
@@ -2100,6 +2030,103 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118846912</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Anders-Jönsmyran, S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>554979</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7013460</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36943-2022 artfynd.xlsx
+++ b/artfynd/A 36943-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846920</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846907</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846914</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846915</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846924</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846926</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846918</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846919</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,8 +2202,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118846912</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>